--- a/KURIKULUM2026_REVISI/044_DEV_REPORT_DAN_LOG_PENYUSUNAN_MATRIKS_CPL_CPMK_BoK_GUARDRAILS.xlsx
+++ b/KURIKULUM2026_REVISI/044_DEV_REPORT_DAN_LOG_PENYUSUNAN_MATRIKS_CPL_CPMK_BoK_GUARDRAILS.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>`STI-624`, `STI-625`, `STI-626`, `STI-627`</t>
+          <t>`STI-726`, `STI-727`, `STI-726`, `STI-727`</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>`STI-624`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>`STI-625`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>`STI-626`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>`STI-627`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
